--- a/rest/schema-diffs/REST-schema-questions-for-developer_2026-08-26.xlsx
+++ b/rest/schema-diffs/REST-schema-questions-for-developer_2026-08-26.xlsx
@@ -1,105 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\fxr60-90-api-docs-main\rest\schema-diffs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AA5123\Desktop\fxr60-90-rest-mqtt-main\rest\schema-diffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F501BC16-280D-4181-9BA0-271548808398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8BB9236-5C73-4779-8416-2020482AF61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="1. Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="2. Questions" sheetId="2" r:id="rId2"/>
-    <sheet name="3. Copy-paste text" sheetId="3" r:id="rId3"/>
+    <sheet name="Questions" sheetId="2" r:id="rId1"/>
+    <sheet name="3. Copy-paste text" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Questions'!$A$2:$I$16</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'1. Summary'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'2. Questions'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Questions!$A$2:$H$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Questions!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="130">
-  <si>
-    <t>REST schema questions for firmware / spec owner</t>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>26 August 2026</t>
-  </si>
-  <si>
-    <t>Product</t>
-  </si>
-  <si>
-    <t>FXR60 / FXR90 REST and MQTT API docs</t>
-  </si>
-  <si>
-    <t>Please</t>
-  </si>
-  <si>
-    <t>Reply in column I on sheet 2. Questions. One row = one question.</t>
-  </si>
-  <si>
-    <t>How we tested</t>
-  </si>
-  <si>
-    <t>Where Tested says Yes, the reader already behaves as described. We kept our docs. We need the OpenAPI spec to match the reader, or a reason not to.</t>
-  </si>
-  <si>
-    <t>Not in this sheet</t>
-  </si>
-  <si>
-    <t>Items we already aligned to your spec (install options, retry/timeouts, DELETE certificate type in body, GET network interface, config xml, start/stop scanType, version, cable loss, readerCapabilities DC). No action needed on those.</t>
-  </si>
-  <si>
-    <t>Question count</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>REST APIs in this sheet</t>
-  </si>
-  <si>
-    <t>1. GET /cloud/mode and PUT /cloud/mode</t>
-  </si>
-  <si>
-    <t>2. PUT /cloud/network and GET /cloud/network</t>
-  </si>
-  <si>
-    <t>3. GET /cloud/config</t>
-  </si>
-  <si>
-    <t>4. PUT /cloud/config</t>
-  </si>
-  <si>
-    <t>5. GET /cloud/stack-led</t>
-  </si>
-  <si>
-    <t>6. GET /cloud/status</t>
-  </si>
-  <si>
-    <t>7. PUT /cloud/certificates and PUT /cloud/os</t>
-  </si>
-  <si>
-    <t>8. PUT /cloud/impinjGen2X</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="97">
   <si>
     <t>Please fill column I (Your reply). Filter and sort are on. One row = one question.</t>
   </si>
@@ -116,9 +42,6 @@
     <t>Topic</t>
   </si>
   <si>
-    <t>Tested on reader?</t>
-  </si>
-  <si>
     <t>What the reader does</t>
   </si>
   <si>
@@ -140,9 +63,6 @@
     <t>verbose request body</t>
   </si>
   <si>
-    <t>Yes — 26 Aug 2026</t>
-  </si>
-  <si>
     <t>{ "verbose": true } works. Full config including defaults is returned.</t>
   </si>
   <si>
@@ -161,9 +81,6 @@
     <t>GPI ports 1–4</t>
   </si>
   <si>
-    <t>Yes — reader has 4 GPI ports (GET /cloud/gpi). readerCapabilities example: numGPIs: 4</t>
-  </si>
-  <si>
     <t>Four GPI ports: 1, 2, 3, and 4.</t>
   </si>
   <si>
@@ -176,9 +93,6 @@
     <t>READER_LOCATION in tagMetaData</t>
   </si>
   <si>
-    <t>Not retested this round. Our docs include it.</t>
-  </si>
-  <si>
     <t>Our docs include READER_LOCATION in tagMetaData.</t>
   </si>
   <si>
@@ -281,9 +195,6 @@
     <t>GET enums vs PUT enums</t>
   </si>
   <si>
-    <t>Not device-tested this round. Asking about the spec.</t>
-  </si>
-  <si>
     <t>PUT lists color: red, amber, green, blue, off. brightness: low, med, high.</t>
   </si>
   <si>
@@ -302,9 +213,6 @@
     <t>Antenna ports 1–8</t>
   </si>
   <si>
-    <t>Not device-tested this round. FXR60 does not have eight antennas.</t>
-  </si>
-  <si>
     <t>FXR60 does not have eight antennas.</t>
   </si>
   <si>
@@ -317,9 +225,6 @@
     <t>impinjGen2X.feature when unused</t>
   </si>
   <si>
-    <t>Not device-tested this round.</t>
-  </si>
-  <si>
     <t>Our docs also consider none when Gen2X is not in use.</t>
   </si>
   <si>
@@ -332,9 +237,6 @@
     <t>powerSource values</t>
   </si>
   <si>
-    <t>Observed on FXR</t>
-  </si>
-  <si>
     <t>PWR_BRICK, POE, and POE+. DC is not used on FXR.</t>
   </si>
   <si>
@@ -351,9 +253,6 @@
   </si>
   <si>
     <t>BASIC credentials key</t>
-  </si>
-  <si>
-    <t>Yes — authenticationOptions works. options does not. (Install uses options; that one is already aligned.)</t>
   </si>
   <si>
     <t>Username and password work with authenticationOptions. options does not work.</t>
@@ -467,7 +366,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -558,7 +457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -575,19 +474,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -889,669 +786,494 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="110" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="28.05" customHeight="1">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11"/>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="22.05" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="22.05" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="48" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="48" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="48" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="48" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
     <col min="3" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="36" customWidth="1"/>
-    <col min="6" max="6" width="48" customWidth="1"/>
-    <col min="7" max="7" width="42" customWidth="1"/>
-    <col min="8" max="8" width="55" customWidth="1"/>
-    <col min="9" max="9" width="40" customWidth="1"/>
+    <col min="5" max="5" width="48" customWidth="1"/>
+    <col min="6" max="6" width="42" customWidth="1"/>
+    <col min="7" max="7" width="55" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="22.05" customHeight="1">
-      <c r="A1" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-    </row>
-    <row r="2" spans="1:9" ht="24" customHeight="1">
+    <row r="1" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+    </row>
+    <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="72" customHeight="1">
-      <c r="A3" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" s="9"/>
-    </row>
-    <row r="4" spans="1:9" ht="72" customHeight="1">
+      <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" s="9"/>
-    </row>
-    <row r="5" spans="1:9" ht="72" customHeight="1">
-      <c r="A5" s="8">
+        <v>20</v>
+      </c>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5" s="9"/>
-    </row>
-    <row r="6" spans="1:9" ht="72" customHeight="1">
+      <c r="B5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I6" s="9"/>
-    </row>
-    <row r="7" spans="1:9" ht="72" customHeight="1">
-      <c r="A7" s="8">
+        <v>30</v>
+      </c>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I7" s="9"/>
-    </row>
-    <row r="8" spans="1:9" ht="72" customHeight="1">
+      <c r="B7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I8" s="9"/>
-    </row>
-    <row r="9" spans="1:9" ht="72" customHeight="1">
-      <c r="A9" s="8">
+        <v>40</v>
+      </c>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="I9" s="9"/>
-    </row>
-    <row r="10" spans="1:9" ht="72" customHeight="1">
+      <c r="B9" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="I10" s="9"/>
-    </row>
-    <row r="11" spans="1:9" ht="72" customHeight="1">
-      <c r="A11" s="8">
+        <v>52</v>
+      </c>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I11" s="9"/>
-    </row>
-    <row r="12" spans="1:9" ht="72" customHeight="1">
+      <c r="B11" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="I12" s="9"/>
-    </row>
-    <row r="13" spans="1:9" ht="72" customHeight="1">
-      <c r="A13" s="8">
+        <v>64</v>
+      </c>
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" spans="1:9" ht="72" customHeight="1">
+      <c r="B13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="I14" s="9"/>
-    </row>
-    <row r="15" spans="1:9" ht="72" customHeight="1">
-      <c r="A15" s="8">
+        <v>72</v>
+      </c>
+      <c r="H14" s="7"/>
+    </row>
+    <row r="15" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="I15" s="9"/>
-    </row>
-    <row r="16" spans="1:9" ht="72" customHeight="1">
+      <c r="B15" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I16" s="9"/>
+        <v>84</v>
+      </c>
+      <c r="H16" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I16" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A2:H16" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
     <col min="2" max="2" width="120" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28.05" customHeight="1">
+    <row r="1" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="B1" s="11"/>
-    </row>
-    <row r="3" spans="1:2">
+        <v>96</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="196.05" customHeight="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="196.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="259.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="259.95" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="84" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="B6" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="67.95" customHeight="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="132" customHeight="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="132" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="180" customHeight="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="180" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="84" customHeight="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="100.05" customHeight="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/rest/schema-diffs/REST-schema-questions-for-developer_2026-08-26.xlsx
+++ b/rest/schema-diffs/REST-schema-questions-for-developer_2026-08-26.xlsx
@@ -508,7 +508,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" style="9" min="1" max="1"/>
     <col width="42" customWidth="1" style="9" min="2" max="2"/>
@@ -1408,17 +1408,17 @@
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Sending the reader's own spec's literal description text ("get_displayCOnfig", capital O) fails with "cannot handle request (invalid command)". get_displayConfig (correct casing) succeeds.</t>
+          <t>During device testing, we confirmed the working MQTT command is get_displayConfig.</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>openAPISpec 10.yaml's description field for this endpoint says get_displayCOnfig.</t>
+          <t>openAPISpec 10.yaml currently lists the MQTT command as get_displayCOnfig (capital O).</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>Can you fix the typo in your spec? We already use the correct casing (get_displayConfig) in our docs and MQTT schema. Note: one test run had a leading space alongside the typo, so we plan one more clean isolation test before treating this as fully proven -- flagging now so you're aware while we finish confirming.</t>
+          <t>Could you please verify and fix this typo in the developer spec? Current: get_displayCOnfig. Correct: get_displayConfig. Our documentation will continue to use get_displayConfig based on device-tested behavior.</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col width="48" customWidth="1" style="9" min="1" max="1"/>
     <col width="120" customWidth="1" style="9" min="2" max="2"/>
@@ -1740,11 +1740,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Sending the exact command text from your spec's own description field ("get_displayCOnfig", capital O) fails with "cannot handle request (invalid command)".
-get_displayConfig (correct casing) succeeds.
-Your openAPISpec 10.yaml's description field for this endpoint says get_displayCOnfig.
-Can you fix the typo? We already use the correct casing (get_displayConfig) in our docs and MQTT schema.
-Note: one of our test runs had a leading space alongside the typo, so we are running one more clean isolation test before treating this as fully proven -- flagging now while we finish confirming.</t>
+          <t>For GET /cloud/displayConfig, openAPISpec 10.yaml currently lists the MQTT command as get_displayCOnfig.
+However, during device testing, we confirmed that the working MQTT command is get_displayConfig.
+Could you please verify and fix this typo in the developer spec?
+Current: get_displayCOnfig
+Correct: get_displayConfig
+Our documentation will continue to use get_displayConfig based on the device-tested behavior.</t>
         </is>
       </c>
     </row>

--- a/rest/schema-diffs/REST-schema-questions-for-developer_2026-08-26.xlsx
+++ b/rest/schema-diffs/REST-schema-questions-for-developer_2026-08-26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Questions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="3. Copy-paste text" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Copy-paste text" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$2:$H$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$2:$H$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Questions'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -56,7 +56,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -83,8 +83,18 @@
         <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -107,11 +117,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -140,6 +156,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -507,8 +529,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" style="9" min="1" max="1"/>
     <col width="42" customWidth="1" style="9" min="2" max="2"/>
@@ -1422,8 +1444,116 @@
         </is>
       </c>
     </row>
+    <row r="27" ht="90" customHeight="1" s="9">
+      <c r="A27" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>PUT /cloud/mode</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>set_mode</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>wordCounter vs wordCount</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>wordCount works in the READ access config. wordCounter is rejected (HTTP 422): "wordCount must be included in access-config object for read". After renaming the field, TID is returned in accessResults.</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>The READ config requires wordCounter. The with_accesses example also uses wordCounter. MQTT set_mode uses the same name. The description on wordCounter repeats "WordPtr Field" (that is wordPointer).</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>Can you change the spec field name from wordCounter to wordCount so it matches the reader?</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="n"/>
+    </row>
+    <row r="28" ht="90" customHeight="1" s="9">
+      <c r="A28" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>PUT /cloud/bleConfig (GET /cloud/bleConfig response: generic filters)</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>set_bleConfig / get_bleConfig</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>generic filter field casing</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>The generic filter accepts only lowercase names: address, addressType, name, alias. Capital names Address, AddressType, Name, Alias are rejected (HTTP 422): unknown or unexpected field. Isolated by bisection on reader 5.0.7. After lowercasing, the same body is stored and read back.</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>PUT schema, PUT example enable_with_protocols, and GET schema/example all use Address, AddressType, Name, Alias. Those look like BLE output event names pasted into the input filter.</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>Can you change the generic filter field names to address, addressType, name, alias in both the schema and the examples (PUT enable_with_protocols and GET)? Same names appear on GET /cloud/bleConfig.</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="n"/>
+    </row>
+    <row r="29" ht="90" customHeight="1" s="9">
+      <c r="A29" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>PUT /cloud/bleConfig</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>set_bleConfig</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>four required ble fields vs description / short examples</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>PUT fails if any of these four is missing: enable, scanIntervalSec, protocols, additionalFilters. A short body such as {"ble":{"enable":true}} is rejected. additionalFilters may be {}. protocols may list only one protocol. All four keys must still be present.</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>The schema required list already has those four fields. The operation description still says only ble.enable is required and the other fields are optional. That wording does not match the schema or the reader.</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>Can you change the description so it says all four fields are required (enable, scanIntervalSec, protocols, additionalFilters), matching the schema and the reader? Please also check that no example omits any of the four — a short example will fail on the device.</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:H26"/>
+  <autoFilter ref="A2:H27"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -1438,8 +1568,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="48" customWidth="1" style="9" min="1" max="1"/>
     <col width="120" customWidth="1" style="9" min="2" max="2"/>
@@ -1749,6 +1879,22 @@
         </is>
       </c>
     </row>
+    <row r="21" ht="90" customHeight="1" s="9">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>PUT /cloud/mode</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>On PUT /cloud/mode, wordCount works in the READ access config.
+wordCounter is rejected (HTTP 422): wordCount must be included in access-config object for read.
+Your spec requires wordCounter (example with_accesses uses the same name).
+MQTT set_mode uses the same name.
+Can you change the spec field name from wordCounter to wordCount so it matches the reader?</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
